--- a/自考本科/课程学习及笔记/Byvm815/考试时间安排表.xlsx
+++ b/自考本科/课程学习及笔记/Byvm815/考试时间安排表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>2026年</t>
   </si>
@@ -27,19 +27,22 @@
     <t>2028年</t>
   </si>
   <si>
+    <t>1月</t>
+  </si>
+  <si>
+    <t>4月</t>
+  </si>
+  <si>
+    <t>10月</t>
+  </si>
+  <si>
     <t>自考科目</t>
   </si>
   <si>
-    <t>1月</t>
-  </si>
-  <si>
-    <t>4月</t>
-  </si>
-  <si>
-    <t>10月</t>
-  </si>
-  <si>
     <t>00023-高等数学（工本）</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t>02324-离散数学</t>
@@ -79,19 +82,25 @@
 中国特色社会主义思想概论</t>
   </si>
   <si>
+    <t>3月</t>
+  </si>
+  <si>
+    <t>9月</t>
+  </si>
+  <si>
     <t>免考科目</t>
   </si>
   <si>
-    <t>3月</t>
-  </si>
-  <si>
-    <t>9月</t>
-  </si>
-  <si>
-    <t>13000-英语（专升本）</t>
-  </si>
-  <si>
-    <t>13014-高级语言程序设计</t>
+    <t xml:space="preserve">公共英语三级（PETS3）
+免考13000-英语（专升本）
+免考学位英语</t>
+  </si>
+  <si>
+    <t xml:space="preserve">计算机二级（NCRE2）
+免考13013-高级语言程序设计</t>
+  </si>
+  <si>
+    <t>8月</t>
   </si>
   <si>
     <t>实践科目</t>
@@ -101,8 +110,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -129,22 +145,25 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -669,178 +688,176 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" ht="14.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="1">
-        <v>1</v>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
+      <c r="A9" s="2"/>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1</v>
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="28.5">
-      <c r="A15" s="1"/>
-      <c r="B15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
+      <c r="A15" s="2"/>
+      <c r="B15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="B17" s="5"/>
       <c r="C17" s="1" t="s">
         <v>21</v>
       </c>
@@ -860,21 +877,26 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="14.25">
-      <c r="B18" s="1" t="s">
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="B19" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
+      <c r="F18" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" ht="25.300000000000001" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="1"/>
     </row>
     <row r="20" ht="14.25">
       <c r="C20" s="1" t="s">
@@ -894,21 +916,55 @@
       <c r="K20" s="1"/>
     </row>
     <row r="21" ht="14.25">
-      <c r="B21" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A3:A15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="F16:H16"/>
     <mergeCell ref="I16:K16"/>
+    <mergeCell ref="A18:A19"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="I20:K20"/>
+    <mergeCell ref="A22:A25"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/自考本科/课程学习及笔记/Byvm815/考试时间安排表.xlsx
+++ b/自考本科/课程学习及笔记/Byvm815/考试时间安排表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>2026年</t>
   </si>
@@ -104,6 +104,19 @@
   </si>
   <si>
     <t>实践科目</t>
+  </si>
+  <si>
+    <t>03345-信息与网络安全管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13004-数据结构与算法
+13014-高级语言程序设计</t>
+  </si>
+  <si>
+    <t>08075-计算机高级程序设计</t>
+  </si>
+  <si>
+    <t>13006-软件工程</t>
   </si>
 </sst>
 </file>
@@ -145,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -164,6 +177,12 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -941,15 +960,39 @@
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" ht="14.25">
+      <c r="B22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" ht="28.5">
       <c r="A23" s="2"/>
+      <c r="B23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="2"/>
+      <c r="B24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="2"/>
+      <c r="B25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/自考本科/课程学习及笔记/Byvm815/考试时间安排表.xlsx
+++ b/自考本科/课程学习及笔记/Byvm815/考试时间安排表.xlsx
@@ -16,7 +16,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+  <si>
+    <t>自考科目</t>
+  </si>
   <si>
     <t>2026年</t>
   </si>
@@ -27,68 +30,80 @@
     <t>2028年</t>
   </si>
   <si>
-    <t>1月</t>
-  </si>
-  <si>
-    <t>4月</t>
-  </si>
-  <si>
-    <t>10月</t>
-  </si>
-  <si>
-    <t>自考科目</t>
+    <t>一月</t>
+  </si>
+  <si>
+    <t>第一天上午</t>
+  </si>
+  <si>
+    <t>第一天下午</t>
+  </si>
+  <si>
+    <t>第二天上午</t>
+  </si>
+  <si>
+    <t>第二天下午</t>
+  </si>
+  <si>
+    <t>03344-信息与网络安全管理</t>
+  </si>
+  <si>
+    <t>08074-计算机高级程序设计</t>
+  </si>
+  <si>
+    <t>13009-数据库原理与技术</t>
+  </si>
+  <si>
+    <t>13011-人工智能与大数据</t>
+  </si>
+  <si>
+    <t>四月</t>
+  </si>
+  <si>
+    <t>15044-马克思主义基本原理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15040-习近平新时代中国
+特色社会主义思想概论</t>
+  </si>
+  <si>
+    <t>15043-中国近现代史纲要</t>
+  </si>
+  <si>
+    <t>13000-英语（专升本）</t>
+  </si>
+  <si>
+    <t>02324-离散数学</t>
   </si>
   <si>
     <t>00023-高等数学（工本）</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>02324-离散数学</t>
-  </si>
-  <si>
-    <t>03344-信息与网络安全管理</t>
-  </si>
-  <si>
-    <t>08074-计算机高级程序设计</t>
+    <t>13180-操作系统</t>
+  </si>
+  <si>
+    <t>13005-软件工程</t>
   </si>
   <si>
     <t>13003-数据结构与算法</t>
   </si>
   <si>
-    <t>13005-软件工程</t>
-  </si>
-  <si>
-    <t>13009-数据库原理与技术</t>
-  </si>
-  <si>
-    <t>13011-人工智能与大数据</t>
-  </si>
-  <si>
     <t>13015-计算机系统原理</t>
   </si>
   <si>
-    <t>13180-操作系统</t>
-  </si>
-  <si>
-    <t>15043-中国近现代史纲要</t>
-  </si>
-  <si>
-    <t>15044-马克思主义基本原理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15040-习近平新时代
-中国特色社会主义思想概论</t>
-  </si>
-  <si>
-    <t>3月</t>
-  </si>
-  <si>
-    <t>9月</t>
+    <t>13013-高级语言程序设计</t>
+  </si>
+  <si>
+    <t>十月</t>
   </si>
   <si>
     <t>免考科目</t>
+  </si>
+  <si>
+    <t>三月</t>
+  </si>
+  <si>
+    <t>九月</t>
   </si>
   <si>
     <t xml:space="preserve">公共英语三级（PETS3）
@@ -100,16 +115,16 @@
 免考13013-高级语言程序设计</t>
   </si>
   <si>
-    <t>8月</t>
-  </si>
-  <si>
     <t>实践科目</t>
   </si>
   <si>
+    <t>八月</t>
+  </si>
+  <si>
     <t>03345-信息与网络安全管理</t>
   </si>
   <si>
-    <t xml:space="preserve">13004-数据结构与算法
+    <t xml:space="preserve">13004-数据结构与算法 &amp;&amp;
 13014-高级语言程序设计</t>
   </si>
   <si>
@@ -123,10 +138,40 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -137,16 +182,295 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.000000"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.000000"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18.000000"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.000000"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.000000"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color indexed="65"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.000000"/>
+      <color indexed="4"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="更纱黑体 SC Light"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="更纱黑体 SC Light"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="更纱黑体 SC Light"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241899"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241899"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241899"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241899"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241899"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431398"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241899"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="14">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -154,48 +478,475 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="5" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="8" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="9" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="11" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="12" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="13" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="14" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="15" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="16" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="17" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="18" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="19" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="20" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="21" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="22" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="23" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="24" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="6" fillId="25" borderId="3" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="26" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="27" borderId="4" numFmtId="0" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="7" fillId="28" borderId="5" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="9" fillId="25" borderId="5" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="10" fillId="29" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="6" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="11" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="12" fillId="0" borderId="7" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="30" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="14" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="15" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="16" fillId="0" borderId="7" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="17" fillId="31" borderId="8" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="32" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="18" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="40">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment textRotation="255" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center"/>
+    </xf>
+    <xf fontId="20" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="19" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="20" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf fontId="20" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf fontId="21" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="21" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf fontId="21" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="19" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="19" fillId="34" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="20" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf fontId="19" fillId="34" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="19" fillId="34" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="19" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center"/>
+    </xf>
+    <xf fontId="19" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="20" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="19" fillId="34" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="19" fillId="34" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="19" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="19" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment textRotation="255" vertical="center"/>
+    </xf>
+    <xf fontId="19" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center"/>
+    </xf>
+    <xf fontId="19" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="19" fillId="34" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf fontId="19" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="19" fillId="34" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -681,337 +1432,878 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.140625"/>
-    <col customWidth="1" min="2" max="2" style="1" width="29.8515625"/>
-    <col min="3" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" style="2" width="9"/>
+    <col customWidth="1" min="2" max="5" style="1" width="28.57421875"/>
+    <col customWidth="1" min="6" max="6" style="1" width="1.7109375"/>
+    <col customWidth="1" min="7" max="10" style="1" width="28.57421875"/>
+    <col customWidth="1" min="11" max="11" style="1" width="1.7109375"/>
+    <col customWidth="1" min="12" max="15" style="1" width="28.57421875"/>
+    <col min="16" max="16384" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+    <row r="1" ht="15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" ht="14.25">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+    </row>
+    <row r="2" ht="15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+    </row>
+    <row r="3" s="9" customFormat="1" ht="15">
+      <c r="A3" s="3"/>
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="11"/>
+      <c r="L3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="12" customFormat="1" ht="15">
+      <c r="A4" s="3"/>
+      <c r="B4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="14"/>
+      <c r="L4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="15">
+      <c r="A5" s="3"/>
+      <c r="B5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+    </row>
+    <row r="6" s="9" customFormat="1" ht="15">
+      <c r="A6" s="3"/>
+      <c r="B6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="12" customFormat="1" ht="30">
+      <c r="A7" s="3"/>
+      <c r="B7" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" s="12" customFormat="1" ht="15">
+      <c r="A8" s="3"/>
+      <c r="B8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="14"/>
+      <c r="L8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="12" customFormat="1" ht="15">
+      <c r="A9" s="3"/>
+      <c r="B9" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="14"/>
+      <c r="L9" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" s="12" customFormat="1" ht="15">
+      <c r="A10" s="3"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+    </row>
+    <row r="11" ht="15">
+      <c r="A11" s="3"/>
+      <c r="B11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+    </row>
+    <row r="12" s="9" customFormat="1" ht="15">
+      <c r="A12" s="3"/>
+      <c r="B12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" s="12" customFormat="1" ht="30">
+      <c r="A13" s="3"/>
+      <c r="B13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="14"/>
+      <c r="G13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="14"/>
+      <c r="L13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="O13" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" s="12" customFormat="1" ht="15">
+      <c r="A14" s="3"/>
+      <c r="B14" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" s="12" customFormat="1" ht="15">
+      <c r="A15" s="3"/>
+      <c r="B15" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="14"/>
+      <c r="L15" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="O15" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" s="12" customFormat="1" ht="15">
+      <c r="A16" s="3"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+    </row>
+    <row r="17" s="22" customFormat="1" ht="15.75">
+      <c r="A17" s="23"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="22"/>
+    </row>
+    <row r="18" s="12" customFormat="1" ht="15">
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="G18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+    </row>
+    <row r="19" s="12" customFormat="1" ht="15">
+      <c r="A19" s="3"/>
+      <c r="B19" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+    </row>
+    <row r="20" s="12" customFormat="1" ht="45">
+      <c r="A20" s="3"/>
+      <c r="B20" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+    </row>
+    <row r="21" s="12" customFormat="1" ht="45">
+      <c r="A21" s="3"/>
+      <c r="B21" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+    </row>
+    <row r="22" s="31" customFormat="1">
+      <c r="A22" s="32"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+    </row>
+    <row r="23" s="34" customFormat="1" ht="15">
+      <c r="A23" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="28.5">
-      <c r="A15" s="2"/>
-      <c r="B15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" ht="25.300000000000001" customHeight="1">
-      <c r="A19" s="2"/>
-      <c r="B19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="C20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="2" t="s">
+      <c r="H23" s="4"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+    </row>
+    <row r="24" s="34" customFormat="1" ht="15">
+      <c r="A24" s="35"/>
+      <c r="B24" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" ht="28.5">
-      <c r="A23" s="2"/>
-      <c r="B23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>8</v>
+      <c r="C24" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="34"/>
+      <c r="G24" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+    </row>
+    <row r="25" ht="15">
+      <c r="A25" s="35"/>
+      <c r="B25" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" ht="30">
+      <c r="A26" s="35"/>
+      <c r="B26" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" ht="15">
+      <c r="A27" s="35"/>
+      <c r="B27" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" s="36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" ht="15">
+      <c r="A28" s="35"/>
+      <c r="B28" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="A22:A25"/>
+  <mergeCells count="21">
+    <mergeCell ref="A1:A16"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="G23:H23"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <printOptions headings="0" gridLines="1"/>
+  <pageMargins left="0.70078740157480313" right="0.70078740157480313" top="0.75196850393700809" bottom="0.75196850393700809" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="13" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/自考本科/课程学习及笔记/Byvm815/考试时间安排表.xlsx
+++ b/自考本科/课程学习及笔记/Byvm815/考试时间安排表.xlsx
@@ -289,7 +289,7 @@
       <name val="更纱黑体 SC Light"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,24 +449,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241899"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor rgb="FFD8D8D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor theme="0" tint="-0.14999847407452621"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -790,11 +796,13 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" vertical="center"/>
     </xf>
-    <xf fontId="20" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="20" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="19" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="5" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="20" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -807,16 +815,12 @@
     <xf fontId="21" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="21" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="19" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="19" fillId="33" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf fontId="19" fillId="34" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -846,6 +850,12 @@
     </xf>
     <xf fontId="19" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="20" fillId="36" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="20" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1457,14 +1467,14 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="1"/>
       <c r="L1" s="6" t="s">
         <v>3</v>
       </c>
@@ -1480,14 +1490,14 @@
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
-      <c r="F2" s="5"/>
+      <c r="F2" s="1"/>
       <c r="G2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
-      <c r="K2" s="5"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="8" t="s">
         <v>4</v>
       </c>
@@ -1509,7 +1519,7 @@
       <c r="E3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="11"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="10" t="s">
         <v>5</v>
       </c>
@@ -1522,7 +1532,7 @@
       <c r="J3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="11"/>
+      <c r="K3" s="9"/>
       <c r="L3" s="10" t="s">
         <v>5</v>
       </c>
@@ -1536,44 +1546,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="12" customFormat="1" ht="15">
+    <row r="4" s="11" customFormat="1" ht="15">
       <c r="A4" s="3"/>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="11"/>
+      <c r="G4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="13" t="s">
+      <c r="K4" s="11"/>
+      <c r="L4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="12" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1585,20 +1595,20 @@
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="16" t="s">
+      <c r="F5" s="1"/>
+      <c r="G5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="16" t="s">
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
     </row>
     <row r="6" s="9" customFormat="1" ht="15">
       <c r="A6" s="3"/>
@@ -1614,7 +1624,7 @@
       <c r="E6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="9"/>
       <c r="G6" s="10" t="s">
         <v>5</v>
       </c>
@@ -1627,7 +1637,7 @@
       <c r="J6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="11"/>
+      <c r="K6" s="9"/>
       <c r="L6" s="10" t="s">
         <v>5</v>
       </c>
@@ -1641,151 +1651,151 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="12" customFormat="1" ht="30">
+    <row r="7" s="11" customFormat="1" ht="30">
       <c r="A7" s="3"/>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="19" t="s">
+      <c r="F7" s="11"/>
+      <c r="G7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="19" t="s">
+      <c r="K7" s="11"/>
+      <c r="L7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="20" t="s">
+      <c r="M7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="19" t="s">
+      <c r="N7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="O7" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" s="12" customFormat="1" ht="15">
+    <row r="8" s="11" customFormat="1" ht="15">
       <c r="A8" s="3"/>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="19" t="s">
+      <c r="F8" s="11"/>
+      <c r="G8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="19" t="s">
+      <c r="K8" s="11"/>
+      <c r="L8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="19" t="s">
+      <c r="N8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="19" t="s">
+      <c r="O8" s="17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" s="12" customFormat="1" ht="15">
+    <row r="9" s="11" customFormat="1" ht="15">
       <c r="A9" s="3"/>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="19" t="s">
+      <c r="F9" s="11"/>
+      <c r="G9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="19" t="s">
+      <c r="K9" s="11"/>
+      <c r="L9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="19" t="s">
+      <c r="N9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" s="12" customFormat="1" ht="15">
+    <row r="10" s="11" customFormat="1" ht="15">
       <c r="A10" s="3"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="13" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="13" t="s">
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
     </row>
     <row r="11" ht="15">
       <c r="A11" s="3"/>
@@ -1795,20 +1805,20 @@
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="16" t="s">
+      <c r="F11" s="1"/>
+      <c r="G11" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="16" t="s">
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
     </row>
     <row r="12" s="9" customFormat="1" ht="15">
       <c r="A12" s="3"/>
@@ -1824,7 +1834,7 @@
       <c r="E12" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="9"/>
       <c r="G12" s="10" t="s">
         <v>5</v>
       </c>
@@ -1837,7 +1847,7 @@
       <c r="J12" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="11"/>
+      <c r="K12" s="9"/>
       <c r="L12" s="10" t="s">
         <v>5</v>
       </c>
@@ -1851,194 +1861,194 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="12" customFormat="1" ht="30">
+    <row r="13" s="11" customFormat="1" ht="30">
       <c r="A13" s="3"/>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="19" t="s">
+      <c r="F13" s="11"/>
+      <c r="G13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="19" t="s">
+      <c r="K13" s="11"/>
+      <c r="L13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="20" t="s">
+      <c r="M13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="N13" s="19" t="s">
+      <c r="N13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="O13" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" s="12" customFormat="1" ht="15">
+    <row r="14" s="11" customFormat="1" ht="15">
       <c r="A14" s="3"/>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="19" t="s">
+      <c r="F14" s="11"/>
+      <c r="G14" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="19" t="s">
+      <c r="J14" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="19" t="s">
+      <c r="K14" s="11"/>
+      <c r="L14" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="N14" s="19" t="s">
+      <c r="N14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="O14" s="19" t="s">
+      <c r="O14" s="17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" s="12" customFormat="1" ht="15">
+    <row r="15" s="11" customFormat="1" ht="15">
       <c r="A15" s="3"/>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="19" t="s">
+      <c r="F15" s="11"/>
+      <c r="G15" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="19" t="s">
+      <c r="K15" s="11"/>
+      <c r="L15" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="19" t="s">
+      <c r="N15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O15" s="19" t="s">
+      <c r="O15" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" s="12" customFormat="1" ht="15">
+    <row r="16" s="11" customFormat="1" ht="15">
       <c r="A16" s="3"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="13" t="s">
+      <c r="B16" s="19"/>
+      <c r="C16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="13" t="s">
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="13" t="s">
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-    </row>
-    <row r="17" s="22" customFormat="1" ht="15.75">
-      <c r="A17" s="23"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="22"/>
-    </row>
-    <row r="18" s="12" customFormat="1" ht="15">
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+    </row>
+    <row r="17" s="20" customFormat="1" ht="15.75">
+      <c r="A17" s="21"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="20"/>
+    </row>
+    <row r="18" s="11" customFormat="1" ht="15">
       <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="G18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="G18" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="23"/>
       <c r="I18" s="25"/>
       <c r="J18" s="25"/>
-      <c r="L18" s="12"/>
+      <c r="L18" s="11"/>
       <c r="M18" s="25"/>
       <c r="N18" s="25"/>
       <c r="O18" s="25"/>
     </row>
-    <row r="19" s="12" customFormat="1" ht="15">
+    <row r="19" s="11" customFormat="1" ht="15">
       <c r="A19" s="3"/>
       <c r="B19" s="26" t="s">
         <v>27</v>
@@ -2060,12 +2070,12 @@
       </c>
       <c r="I19" s="25"/>
       <c r="J19" s="25"/>
-      <c r="L19" s="12"/>
+      <c r="L19" s="11"/>
       <c r="M19" s="25"/>
       <c r="N19" s="25"/>
       <c r="O19" s="25"/>
     </row>
-    <row r="20" s="12" customFormat="1" ht="45">
+    <row r="20" s="11" customFormat="1" ht="45">
       <c r="A20" s="3"/>
       <c r="B20" s="27" t="s">
         <v>29</v>
@@ -2087,12 +2097,12 @@
       </c>
       <c r="I20" s="25"/>
       <c r="J20" s="25"/>
-      <c r="L20" s="12"/>
+      <c r="L20" s="11"/>
       <c r="M20" s="25"/>
       <c r="N20" s="25"/>
       <c r="O20" s="25"/>
     </row>
-    <row r="21" s="12" customFormat="1" ht="45">
+    <row r="21" s="11" customFormat="1" ht="45">
       <c r="A21" s="3"/>
       <c r="B21" s="29" t="s">
         <v>30</v>
@@ -2114,7 +2124,7 @@
       </c>
       <c r="I21" s="25"/>
       <c r="J21" s="25"/>
-      <c r="L21" s="12"/>
+      <c r="L21" s="11"/>
       <c r="M21" s="25"/>
       <c r="N21" s="25"/>
       <c r="O21" s="25"/>
@@ -2141,19 +2151,19 @@
       <c r="A23" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="34"/>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="H23" s="4"/>
+      <c r="H23" s="23"/>
       <c r="I23" s="34"/>
       <c r="J23" s="34"/>
       <c r="K23" s="34"/>
